--- a/Forest字典.xlsx
+++ b/Forest字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E2DA0-90AE-4BB3-A123-D15BF914A634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3235D3-36D3-49B7-9D30-962ABF7FF68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="78">
   <si>
     <t>UA名字</t>
   </si>
@@ -257,6 +257,10 @@
   </si>
   <si>
     <t>0988</t>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -290,6 +294,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -297,6 +302,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -628,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1186,6 +1192,11 @@
         <v>65</v>
       </c>
     </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Forest字典.xlsx
+++ b/Forest字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3235D3-36D3-49B7-9D30-962ABF7FF68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1EE966-465A-4373-80FD-38543521B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
   <si>
     <t>UA名字</t>
   </si>
@@ -257,10 +257,6 @@
   </si>
   <si>
     <t>0988</t>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -634,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1192,11 +1188,6 @@
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Forest字典.xlsx
+++ b/Forest字典.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1EE966-465A-4373-80FD-38543521B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35260FF5-3A14-4992-8256-F84CE90CFCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="79">
   <si>
     <t>UA名字</t>
   </si>
@@ -241,9 +250,6 @@
     <t>1389</t>
   </si>
   <si>
-    <t>2989</t>
-  </si>
-  <si>
     <t>5087</t>
   </si>
   <si>
@@ -257,13 +263,22 @@
   </si>
   <si>
     <t>0988</t>
+  </si>
+  <si>
+    <t>9823</t>
+  </si>
+  <si>
+    <t>4954</t>
+  </si>
+  <si>
+    <t>4360</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,14 +288,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -338,16 +345,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -645,547 +649,563 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="4" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="1" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Forest字典.xlsx
+++ b/Forest字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35260FF5-3A14-4992-8256-F84CE90CFCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7213435A-A09F-4BD0-A3F0-0AF7BE097F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
   <si>
     <t>UA名字</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>4360</t>
+  </si>
+  <si>
+    <t>2989</t>
   </si>
 </sst>
 </file>
@@ -634,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -985,11 +988,11 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>38</v>
+      <c r="A44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -997,7 +1000,7 @@
         <v>37</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1005,7 +1008,7 @@
         <v>37</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1013,7 +1016,7 @@
         <v>37</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1021,7 +1024,7 @@
         <v>37</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1029,7 +1032,7 @@
         <v>37</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1037,7 +1040,7 @@
         <v>37</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1045,7 +1048,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1053,7 +1056,7 @@
         <v>37</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1061,7 +1064,7 @@
         <v>37</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1069,7 +1072,7 @@
         <v>37</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1077,7 +1080,7 @@
         <v>37</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1085,15 +1088,15 @@
         <v>37</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1101,7 +1104,7 @@
         <v>50</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1109,7 +1112,7 @@
         <v>50</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1117,7 +1120,7 @@
         <v>50</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -1125,7 +1128,7 @@
         <v>50</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -1133,7 +1136,7 @@
         <v>50</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1141,7 +1144,7 @@
         <v>50</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1149,7 +1152,7 @@
         <v>50</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -1157,7 +1160,7 @@
         <v>50</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -1165,23 +1168,23 @@
         <v>50</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -1189,7 +1192,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1197,7 +1200,7 @@
         <v>63</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -1205,6 +1208,14 @@
         <v>63</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>78</v>
       </c>
     </row>

--- a/Forest字典.xlsx
+++ b/Forest字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7213435A-A09F-4BD0-A3F0-0AF7BE097F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2909B219-769A-46FB-9D37-601CDADD0726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
   <si>
     <t>UA名字</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>2989</t>
+  </si>
+  <si>
+    <t>6895</t>
+  </si>
+  <si>
+    <t>1370</t>
   </si>
 </sst>
 </file>
@@ -637,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1219,6 +1225,22 @@
         <v>78</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
